--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_100_R10.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_100_R10.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5296</v>
+        <v>7.7925</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1993</v>
+        <v>7.2731</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3303</v>
+        <v>0.5193</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5646</v>
+        <v>8.548400000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8714</v>
+        <v>1.8834</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6932</v>
+        <v>6.665</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7109</v>
+        <v>7.0979</v>
       </c>
       <c r="K2" t="n">
-        <v>3.0116</v>
+        <v>1.7414</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6993</v>
+        <v>5.3566</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8537</v>
+        <v>1.4504</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1401</v>
+        <v>0.142</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9939</v>
+        <v>1.3084</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8206</v>
+        <v>-1.3074</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8259</v>
+        <v>-0.4125</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0053</v>
+        <v>-0.8948</v>
       </c>
       <c r="V2" t="n">
-        <v>2.6805</v>
+        <v>-1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8223</v>
+        <v>0.8197</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1418</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.7487</v>
+        <v>7.2842</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5654</v>
+        <v>5.4916</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1833</v>
+        <v>1.7926</v>
       </c>
       <c r="G3" t="n">
-        <v>8.548400000000001</v>
+        <v>4.5646</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8834</v>
+        <v>2.8714</v>
       </c>
       <c r="I3" t="n">
-        <v>6.665</v>
+        <v>1.6932</v>
       </c>
       <c r="J3" t="n">
-        <v>7.0979</v>
+        <v>3.7109</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7414</v>
+        <v>3.0116</v>
       </c>
       <c r="L3" t="n">
-        <v>5.3566</v>
+        <v>0.6993</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4504</v>
+        <v>0.8537</v>
       </c>
       <c r="N3" t="n">
-        <v>0.142</v>
+        <v>-0.1401</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3084</v>
+        <v>0.9939</v>
       </c>
       <c r="P3" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.6237</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.8556</v>
-      </c>
       <c r="S3" t="n">
-        <v>-2.3511</v>
+        <v>-0.4248</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1202</v>
+        <v>0.1182</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2309</v>
+        <v>-0.543</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0722</v>
+        <v>2.6805</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8197</v>
+        <v>2.8223</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.8919</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5949</v>
+        <v>1.6919</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0301</v>
+        <v>2.4967</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4352</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>3.4425</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9747</v>
+        <v>0.0716</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2492</v>
+        <v>0.7158</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2745</v>
+        <v>-0.6442</v>
       </c>
       <c r="V4" t="n">
         <v>-2.2862</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.644</v>
+        <v>1.5913</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8502999999999999</v>
+        <v>-0.0519</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7937</v>
+        <v>1.6432</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0389</v>
+        <v>3.0823</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9087</v>
+        <v>0.8739</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8699</v>
+        <v>2.2084</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1178</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2708</v>
+        <v>0.1953</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3887</v>
+        <v>0.4282</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1567</v>
+        <v>2.4587</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3621</v>
+        <v>0.6785</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5188</v>
+        <v>1.7802</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3769</v>
+        <v>-1.0941</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3778</v>
+        <v>0.2008</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7547</v>
+        <v>-1.2948</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7501</v>
+        <v>-1.3247</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7501</v>
+        <v>0.2836</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>S. LEE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9857</v>
+        <v>1.0053</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2878</v>
+        <v>2.3155</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2735</v>
+        <v>-1.3103</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0823</v>
+        <v>0.2341</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8739</v>
+        <v>1.0372</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2084</v>
+        <v>-0.8031</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.8133</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1953</v>
+        <v>1.5629</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4282</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>2.4587</v>
+        <v>-0.5792</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6785</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>1.7802</v>
+        <v>-0.0535</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0876</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6996</v>
+        <v>-0.1592</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0351</v>
+        <v>-0.1061</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.6645</v>
+        <v>-0.0532</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3247</v>
+        <v>0.9304</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2836</v>
+        <v>1.6083</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6083</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. LEE</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9545</v>
+        <v>0.6341</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1976</v>
+        <v>-2.2149</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.243</v>
+        <v>2.849</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2341</v>
+        <v>1.1512</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0372</v>
+        <v>-1.1475</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8031</v>
+        <v>2.2987</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8133</v>
+        <v>-0.8892</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5629</v>
+        <v>-1.3542</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.465</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5792</v>
+        <v>2.0404</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5256999999999999</v>
+        <v>0.2067</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0535</v>
+        <v>1.8337</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.21</v>
+        <v>-1.1255</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.224</v>
+        <v>-0.0784</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0141</v>
+        <v>-1.0471</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9304</v>
+        <v>1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. EVANS</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3383</v>
+        <v>0.5837</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0211</v>
+        <v>0.2605</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3593</v>
+        <v>0.3232</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6827</v>
+        <v>0.0389</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0168</v>
+        <v>0.9087</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6659</v>
+        <v>-0.8699</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0536</v>
+        <v>-0.1178</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0168</v>
+        <v>1.2708</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>-1.3887</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6291</v>
+        <v>0.1567</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.3621</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6291</v>
+        <v>0.5188</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3444</v>
+        <v>-1.4372</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0747</v>
+        <v>-0.212</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2697</v>
+        <v>-1.2252</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2479</v>
+        <v>0.4954</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.097</v>
+        <v>-1.3903</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3449</v>
+        <v>1.8857</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1512</v>
+        <v>1.6058</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1475</v>
+        <v>1.3146</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2987</v>
+        <v>0.2912</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8892</v>
+        <v>-0.0027</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3542</v>
+        <v>0.9075</v>
       </c>
       <c r="L9" t="n">
-        <v>0.465</v>
+        <v>-0.9102</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0404</v>
+        <v>1.6085</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2067</v>
+        <v>0.4071</v>
       </c>
       <c r="O9" t="n">
-        <v>1.8337</v>
+        <v>1.2014</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5116</v>
+        <v>-0.5948</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0395</v>
+        <v>0.0042</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.5512</v>
+        <v>-0.599</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0722</v>
+        <v>-0.2836</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>K. EVANS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1622</v>
+        <v>0.4055</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2159</v>
+        <v>-0.0211</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0537</v>
+        <v>0.4266</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6058</v>
+        <v>0.6827</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3146</v>
+        <v>0.0168</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2912</v>
+        <v>0.6659</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0027</v>
+        <v>0.0536</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9075</v>
+        <v>0.0168</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9102</v>
+        <v>0.0368</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6085</v>
+        <v>0.6291</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4071</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2014</v>
+        <v>0.6291</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2524</v>
+        <v>-0.2772</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8215</v>
+        <v>-0.0747</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4309</v>
+        <v>-0.2025</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.743</v>
+        <v>-0.5579</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0621</v>
+        <v>0.0558</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.6137</v>
       </c>
       <c r="G11" t="n">
         <v>-0.324</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4191</v>
+        <v>-0.2339</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2697</v>
+        <v>-0.2025</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4868</v>
+        <v>-2.4696</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2983</v>
+        <v>-3.1804</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8116</v>
+        <v>0.7108</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9008</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8026</v>
+        <v>-0.7855</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0395</v>
+        <v>0.1575</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8421</v>
+        <v>-0.9429</v>
       </c>
       <c r="V12" t="n">
         <v>1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1547</v>
+        <v>-2.9594</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.032</v>
+        <v>-3.2063</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1228</v>
+        <v>0.2469</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3573</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.849</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6721</v>
+        <v>0.1535</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1769</v>
+        <v>-0.8072</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7886</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.49690000000001</v>
+        <v>15.497</v>
       </c>
       <c r="E14" t="n">
-        <v>7.8285</v>
+        <v>7.8283</v>
       </c>
       <c r="F14" t="n">
         <v>7.6684</v>
@@ -1525,7 +1525,7 @@
         <v>9.264900000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>1.086600000000001</v>
+        <v>1.0866</v>
       </c>
       <c r="M14" t="n">
         <v>11.4169</v>
@@ -1537,7 +1537,7 @@
         <v>10.19</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="Q14" t="n">
         <v>-11.5978</v>
@@ -1546,19 +1546,19 @@
         <v>11.5978</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.0214</v>
+        <v>-8.021699999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4349000000000004</v>
+        <v>0.4349</v>
       </c>
       <c r="U14" t="n">
-        <v>-8.456300000000002</v>
+        <v>-8.4564</v>
       </c>
       <c r="V14" t="n">
         <v>1.7501</v>
       </c>
       <c r="W14" t="n">
-        <v>8.639800000000001</v>
+        <v>8.639799999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-6.8897</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0865</v>
+        <v>1.6819</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4997</v>
+        <v>1.0279</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5869</v>
+        <v>0.6541</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2452</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4014</v>
+        <v>0.9968</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5534</v>
+        <v>1.0815</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.152</v>
+        <v>-0.0848</v>
       </c>
       <c r="V16" t="n">
         <v>0.9304</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1184</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5553</v>
+        <v>0.2409</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4369</v>
+        <v>0.2777</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5529</v>
+        <v>-0.2889</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.311</v>
+        <v>0.929</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.2418</v>
+        <v>-1.218</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5401</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1196</v>
+        <v>1.3514</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.6597</v>
+        <v>-2.2118</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0127</v>
+        <v>0.5715</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4306</v>
+        <v>-0.4223</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5821</v>
+        <v>0.9939</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1558</v>
+        <v>1.1659</v>
       </c>
       <c r="T17" t="n">
-        <v>3.8298</v>
+        <v>1.1013</v>
       </c>
       <c r="U17" t="n">
-        <v>0.326</v>
+        <v>0.0646</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2525</v>
+        <v>-1.7501</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4254</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8217</v>
+        <v>0.0951</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4768</v>
+        <v>-0.4053</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3449</v>
+        <v>0.5004</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2889</v>
+        <v>-0.4797</v>
       </c>
       <c r="H18" t="n">
-        <v>0.929</v>
+        <v>-1.2125</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.218</v>
+        <v>0.7328</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-1.5055</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3514</v>
+        <v>-1.5055</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.2118</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5715</v>
+        <v>1.0258</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4223</v>
+        <v>0.293</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9939</v>
+        <v>0.7328</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>1.469</v>
+        <v>0.0413</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3372</v>
+        <v>-0.1138</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1318</v>
+        <v>0.1551</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.7501</v>
+        <v>-0.3943</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7501</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5327</v>
+        <v>-0.2567</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1694</v>
+        <v>-1.2638</v>
       </c>
       <c r="F19" t="n">
-        <v>0.702</v>
+        <v>1.0071</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4797</v>
+        <v>-0.3551</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2125</v>
+        <v>-0.2245</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7328</v>
+        <v>-0.1306</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5055</v>
+        <v>-0.5407</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5055</v>
+        <v>0.3228</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.8635</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0258</v>
+        <v>0.1856</v>
       </c>
       <c r="N19" t="n">
-        <v>0.293</v>
+        <v>-0.5473</v>
       </c>
       <c r="O19" t="n">
         <v>0.7328</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4788</v>
+        <v>0.5623</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1221</v>
+        <v>0.4367</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3567</v>
+        <v>0.1256</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3348</v>
+        <v>-1.0014</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2074</v>
+        <v>0.9575</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8726</v>
+        <v>-1.9589</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3551</v>
+        <v>-2.3189</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2245</v>
+        <v>-1.228</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1306</v>
+        <v>-1.0908</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5407</v>
+        <v>0.4802</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3228</v>
+        <v>0.3599</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8635</v>
+        <v>0.1203</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1856</v>
+        <v>-2.7991</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5473</v>
+        <v>-1.5879</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7328</v>
+        <v>-1.2112</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4639</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5157</v>
+        <v>-0.0951</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.507</v>
+        <v>0.4564</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.5515</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3.5002</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.5002</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9443</v>
+        <v>-1.1049</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2498</v>
+        <v>0.668</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1942</v>
+        <v>-1.7729</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3189</v>
+        <v>-2.5529</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.228</v>
+        <v>-0.311</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0908</v>
+        <v>-2.2418</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4802</v>
+        <v>-0.5401</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3599</v>
+        <v>1.1196</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1203</v>
+        <v>-1.6597</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7991</v>
+        <v>-2.0127</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5879</v>
+        <v>-1.4306</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2112</v>
+        <v>-0.5821</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0876</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0381</v>
+        <v>1.9325</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2513</v>
+        <v>1.9426</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.0101</v>
       </c>
       <c r="V21" t="n">
-        <v>3.5002</v>
+        <v>-0.2525</v>
       </c>
       <c r="W21" t="n">
-        <v>3.5002</v>
+        <v>0.4254</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5376</v>
+        <v>-2.9923</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.68</v>
+        <v>-2.0338</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8577</v>
+        <v>-0.9585</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0352</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4976</v>
+        <v>1.0429</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2898</v>
+        <v>0.9359</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2078</v>
+        <v>0.107</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>K. MIKALAUSKAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6289</v>
+        <v>-3.3071</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2822</v>
+        <v>-1.0872</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3467</v>
+        <v>-2.2199</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.6267</v>
+        <v>-1.0139</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.1273</v>
+        <v>0.1874</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.4995</v>
+        <v>-1.2012</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8919</v>
+        <v>-1.3783</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3929</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4991</v>
+        <v>-1.4623</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.7348</v>
+        <v>0.3644</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7344</v>
+        <v>0.1034</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0004</v>
+        <v>0.261</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.232</v>
+        <v>0.232</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>1.9773</v>
+        <v>0.1553</v>
       </c>
       <c r="T23" t="n">
-        <v>1.7695</v>
+        <v>0.291</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2078</v>
+        <v>-0.1357</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2525</v>
+        <v>-2.6805</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.2525</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K. MIKALAUSKAS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0985</v>
+        <v>-3.5553</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.677</v>
+        <v>-2.1079</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4215</v>
+        <v>-1.4475</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0139</v>
+        <v>-4.6267</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1874</v>
+        <v>-2.1273</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2012</v>
+        <v>-2.4995</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3783</v>
+        <v>-1.8919</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.3929</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4623</v>
+        <v>-1.4991</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3644</v>
+        <v>-2.7348</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1034</v>
+        <v>-1.7344</v>
       </c>
       <c r="O24" t="n">
-        <v>0.261</v>
+        <v>-1.0004</v>
       </c>
       <c r="P24" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6361</v>
+        <v>1.0508</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2987</v>
+        <v>0.9438</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3374</v>
+        <v>0.107</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.6805</v>
+        <v>0.2525</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.6805</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.1203</v>
+        <v>-4.3111</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3601</v>
+        <v>-2.4165</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7602</v>
+        <v>-1.8946</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6285</v>
@@ -2404,13 +2404,13 @@
         <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6361</v>
+        <v>0.1731</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6642</v>
+        <v>0.2794</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0281</v>
+        <v>-0.1063</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.5795</v>
+        <v>-4.4514</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.6054</v>
+        <v>-4.7797</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0259</v>
+        <v>0.3283</v>
       </c>
       <c r="G26" t="n">
         <v>-4.9905</v>
@@ -2482,13 +2482,13 @@
         <v>1.8556</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6945</v>
+        <v>0.4336</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4832</v>
+        <v>0.3424</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2113</v>
+        <v>0.0912</v>
       </c>
       <c r="V26" t="n">
         <v>-1.7501</v>
@@ -2518,10 +2518,10 @@
         <v>-15.497</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.6685</v>
+        <v>-7.668499999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.8286</v>
+        <v>-7.828399999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-21.7684</v>
@@ -2563,19 +2563,19 @@
         <v>8.021699999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>8.4565</v>
+        <v>8.456300000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4349</v>
+        <v>-0.4347</v>
       </c>
       <c r="V27" t="n">
         <v>-1.7501</v>
       </c>
       <c r="W27" t="n">
-        <v>6.889699999999999</v>
+        <v>6.8897</v>
       </c>
       <c r="X27" t="n">
-        <v>-8.639799999999999</v>
+        <v>-8.639800000000001</v>
       </c>
     </row>
   </sheetData>
